--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G291"/>
+  <dimension ref="A1:G294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer – Healthcare Systems &amp; Automation (On-Site Brooklyn, NY)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>True Care</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9f3b83186e48</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,24 +4266,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
@@ -4598,17 +4598,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,69 +6786,69 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
@@ -8728,17 +8728,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,24 +8756,24 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,24 +8791,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -10541,24 +10541,24 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -10576,40 +10576,145 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect Consultant</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>CG Infinity</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Sugar Land, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
           <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>Incyte Corporation</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
-      <c r="D291" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E291" t="inlineStr">
+      <c r="D294" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E294" t="inlineStr">
         <is>
           <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
+      <c r="F294" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
+      <c r="G294" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G294"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,24 +4441,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,42 +6821,42 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,94 +6866,94 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,34 +8571,34 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,34 +8606,34 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,34 +8641,34 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,34 +8676,34 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,34 +8711,34 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,24 +8756,24 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,34 +8781,34 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,34 +8816,34 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,34 +8851,34 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,34 +8886,34 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8921,34 +8921,34 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8956,34 +8956,34 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,17 +8991,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -10646,24 +10646,24 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -10681,24 +10681,24 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -10706,17 +10706,87 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G296"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,24 +4441,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
@@ -4773,17 +4773,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,69 +6891,69 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,34 +8466,34 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,34 +8501,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,34 +8536,34 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,34 +8571,34 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,34 +8606,34 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,34 +8676,34 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,34 +8711,34 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,24 +8966,24 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,17 +8991,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -10750,41 +10750,6 @@
         </is>
       </c>
       <c r="G295" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D296" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G295"/>
+  <dimension ref="A1:G280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Technical Data Security Architect- Remote (Anywhere in the U.S.)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>GuidePoint Security</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, S3, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eedea720bd23228</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8acbe5f71af378</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Technical Data Security Architect- Remote (Anywhere in the U.S.)</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GuidePoint Security</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8acbe5f71af378</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
+          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
+          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,32 +6411,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,444 +6481,444 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,24 +7881,24 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,34 +7976,34 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,34 +8011,34 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,34 +8046,34 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,34 +8081,34 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,17 +8116,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,34 +8466,34 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,34 +8501,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,34 +8676,34 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,34 +8711,34 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,34 +8746,34 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,34 +8781,34 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,34 +8816,34 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,34 +8851,34 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,34 +8886,34 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8921,34 +8921,34 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -10225,531 +10225,6 @@
         </is>
       </c>
       <c r="G280" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Jericho, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D284" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D285" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D286" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D287" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D288" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D289" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D290" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D291" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D292" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D293" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D294" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D295" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G280"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,17 +6541,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,34 +7976,34 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,17 +8116,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,34 +8466,34 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,34 +8501,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,17 +8536,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -10208,23 +10208,128 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
           <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
-      <c r="D280" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E280" t="inlineStr">
+      <c r="D283" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E283" t="inlineStr">
         <is>
           <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,77 +2656,77 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
@@ -6278,17 +6278,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
@@ -7748,17 +7748,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,34 +7766,34 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,34 +8046,34 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G283"/>
+  <dimension ref="A1:G280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Technical Data Security Architect- Remote (Anywhere in the U.S.)</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GuidePoint Security</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8acbe5f71af378</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
+          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
+          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
+          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,77 +2656,77 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,19 +6131,19 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6208,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,17 +6541,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,24 +7636,24 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,34 +7696,34 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,34 +7731,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,34 +7976,34 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,34 +8396,34 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,34 +8431,34 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,34 +8466,34 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,34 +8501,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,17 +8536,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -10225,111 +10225,6 @@
         </is>
       </c>
       <c r="G280" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G280"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
+          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
+          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,77 +2621,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,77 +2971,77 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,32 +6271,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,17 +6436,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,34 +7486,34 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,34 +7696,34 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,34 +7731,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,34 +7766,34 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,17 +7801,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -10155,76 +10155,6 @@
         </is>
       </c>
       <c r="G278" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D280" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,69 +2936,69 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,19 +6026,19 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
@@ -6208,25 +6208,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,34 +7486,34 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,34 +7696,34 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,24 +8196,24 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,34 +8221,34 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,34 +8256,34 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,34 +8291,34 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,34 +8326,34 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,17 +8361,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -9980,181 +9980,6 @@
         </is>
       </c>
       <c r="G273" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D276" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D278" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G273"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,49 +496,49 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,42 +4231,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,67 +6061,67 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6148,15 +6148,15 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,59 +6166,59 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,34 +6611,34 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,34 +7066,34 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,34 +7101,34 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,34 +7171,34 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,34 +7206,34 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,34 +7696,34 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,34 +7731,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,34 +7766,34 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,34 +7976,34 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,34 +8011,34 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,1940 +8046,15 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Mechanicsburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Lake Mary, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Jericho, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Platform &amp; Engineering Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Engineering Specialist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9b926ab26ddab0</t>
+          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DataOps Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>DevOps and Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3a64edd10b382d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763176f96a31cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ce98541dfda3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d62839de03aa1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb2f81cf1a3538f</t>
+          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7836e19fce928abe</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2c792cb6805dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711cb672af3b8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec2366f3e5f33c5</t>
+          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be535d50bb5dcfa</t>
+          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cbde7bed1667fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecf506d02f7b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19066aad562ac4b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36166cd1f48d6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c81d72d06957622</t>
+          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0ebeb7173af280</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52f6ee8bb1982c</t>
+          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70529a6666bd350</t>
+          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b656260aa5816</t>
+          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494845393944a6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e67f1e5d5f8b579</t>
+          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9888dfbacbe5428</t>
+          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655b6c7ebea9a1da</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62025a89d016617</t>
+          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d095a679571fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e7d5de1a55ab67</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e99afb09d2ba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89022ec4c644a826</t>
+          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b5d7d6c67b694</t>
+          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d29535e8da716c0</t>
+          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bba9e6d37ed0103</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad382164d2dae40</t>
+          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961eb1e067e1a415</t>
+          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfbeb87c4c3781b</t>
+          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9747980ad854de3</t>
+          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a19889388bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b58000b2c14130</t>
+          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2719929d1f2b6f73</t>
+          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ea7cb431027a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ec4a2de2e420d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6538853e1a7f260</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090c835f1d369e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd72294d85302d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc3eca7302ed122</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7d3a92c82c7700</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a05e99de85e8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Engineer - DevSecOps 3 (contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ridley Park, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps 3 (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ridley Park, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd372e8ae9909ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,15 +3943,15 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,15 +3978,15 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,15 +4013,15 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4048,15 +4048,15 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,32 +5711,32 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,102 +5746,102 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,67 +5851,67 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,67 +5921,67 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7670,391 +7670,6 @@
         </is>
       </c>
       <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,15 +3768,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,15 +3803,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,15 +3838,15 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,42 +3891,42 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,129 +5536,129 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7495,181 +7495,6 @@
         </is>
       </c>
       <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>

--- a/results/job_matches_2026-05-23.xlsx
+++ b/results/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca8ade31010ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43d2f73f3f7cb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a3b020afc18655</t>
+          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf894ce120c2902</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e0369107b75bae</t>
+          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d118276c832f8ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c656da40e0268c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a32fd39405533</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebc60984d33e95b</t>
+          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2788e723bf018198</t>
+          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6339c6a3f47a81c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285e6741eff7e39</t>
+          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44186af082e59355</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdefad5bb9de16f</t>
+          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5220ad387db4e712</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf809f6096f7d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0e2275e0d61101</t>
+          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862021cda83aa2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b0fc34897e8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e507e4f162f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233568a8e1b7fd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dcafd0a6147fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf2acdf378380a</t>
+          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672419511bf76525</t>
+          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ff4522c085372c</t>
+          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25971158249414c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f50bed1c5e7d319</t>
+          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95dfc57ee3b0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e32b28a86eea62</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1484adfca26a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8dd82c948c6f13</t>
+          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df27aa62dee4cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,52 +3706,52 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f279f9da97ef984c</t>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51342b09136042d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5732c832077cee8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d38f598430f9a90</t>
+          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c77496eb64e7ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7952d9c50d0a14a</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6fdeb5ae043373</t>
+          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf1f76addc3441d</t>
+          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2076ca28b8b5b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9e22fda137c29</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2b68bda4becc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0583f4ebb0da65</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb46e14348f37e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d647b976e05a7799</t>
+          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907011653de26c28</t>
+          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82908d4dbdf2cdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48593df2c11b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b885683bbeba15e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b8dbbb357997f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b753f8d435f0ddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d835aac1f64897</t>
+          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5864618d1dc94c27</t>
+          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ceb0d98f455dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1291d862dee2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e666548cbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd29c6f2dc94eff</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c18a2feb3c96f24</t>
+          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5552671542f03bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb665d508caace0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ae291cc396ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1b12bf899ed5a</t>
+          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ce32527b75338</t>
+          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58104245a72c11f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a17eb2817a5c616</t>
+          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176e9892f20a2600</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd450da1239a81</t>
+          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067dfdea9df65ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2476676854402c56</t>
+          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fd683cee5f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b999763bff4de3</t>
+          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38301c2ebe4c437</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4502cf85b36aed</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4d0856c1db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a9ef0bc7c86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a652c5bbcbf1b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2206a47ad929dcfe</t>
+          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5517eda799e27619</t>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AI Solutions Analyst</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Vertex AI, Hive, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,42 +5421,42 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DATA ENGINEER II</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DATA ENGINEER II</t>
+          <t>Geospatial Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Geospatial Data Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, Airflow, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1429db835fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Senior QA Analyst/Software</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior QA Analyst/Software</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7460,41 +7460,6 @@
         </is>
       </c>
       <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Cyber Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
         </is>
